--- a/docs/downloads/04/tbl_cm_chars_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_chars_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -827,12 +827,6 @@
           <t>Célibataire</t>
         </is>
       </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -893,7 +887,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D25">
@@ -965,12 +959,6 @@
           <t>Célibataire</t>
         </is>
       </c>
-      <c r="D28">
-        <v>2</v>
-      </c>
-      <c r="E28">
-        <v>1.6</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1031,14 +1019,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E31">
-        <v>7.3</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="32">
@@ -1054,14 +1042,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Marié(e) religieusement</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="E32">
-        <v>0.8</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="33">
@@ -1077,20 +1065,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Marié(e) selon la tradition</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D33">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="E33">
-        <v>50.4</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1100,14 +1088,8 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Veuf(ve)</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>19</v>
-      </c>
-      <c r="E34">
-        <v>15.4</v>
+          <t>Célibataire</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1123,14 +1105,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Divorcé(e)</t>
         </is>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E35">
-        <v>0.7</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="36">
@@ -1146,14 +1128,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Divorcé(e)</t>
+          <t>En concubinage</t>
         </is>
       </c>
       <c r="D36">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E36">
-        <v>18.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="37">
@@ -1169,14 +1151,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>En concubinage</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D37">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E37">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="38">
@@ -1192,14 +1174,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D38">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="E38">
-        <v>4.4</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39">
@@ -1215,20 +1197,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Marié(e) selon la tradition</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D39">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="E39">
-        <v>62</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1238,14 +1220,8 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Veuf(ve)</t>
-        </is>
-      </c>
-      <c r="D40">
-        <v>11</v>
-      </c>
-      <c r="E40">
-        <v>8</v>
+          <t>Célibataire</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -1261,14 +1237,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Divorcé(e)</t>
         </is>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E41">
-        <v>2.6</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="42">
@@ -1284,14 +1260,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Divorcé(e)</t>
+          <t>En concubinage</t>
         </is>
       </c>
       <c r="D42">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E42">
-        <v>12.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
@@ -1307,14 +1283,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>En concubinage</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E43">
-        <v>6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="44">
@@ -1330,14 +1306,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D44">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="E44">
-        <v>5.2</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="45">
@@ -1353,20 +1329,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Marié(e) religieusement</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E45">
-        <v>1.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1376,20 +1352,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Marié(e) selon la tradition</t>
+          <t>Célibataire</t>
         </is>
       </c>
       <c r="D46">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="E46">
-        <v>65.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1399,14 +1375,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Veuf(ve)</t>
+          <t>Divorcé(e)</t>
         </is>
       </c>
       <c r="D47">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="E47">
-        <v>6.9</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="48">
@@ -1422,14 +1398,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>En concubinage</t>
         </is>
       </c>
       <c r="D48">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E48">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="49">
@@ -1445,14 +1421,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Divorcé(e)</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D49">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="E49">
-        <v>16.2</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="50">
@@ -1468,14 +1444,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>En concubinage</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D50">
-        <v>32</v>
+        <v>317</v>
       </c>
       <c r="E50">
-        <v>6.2</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="51">
@@ -1491,82 +1467,13 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D51">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="E51">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Marié(e) religieusement</t>
-        </is>
-      </c>
-      <c r="D52">
-        <v>3</v>
-      </c>
-      <c r="E52">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Marié(e) selon la tradition</t>
-        </is>
-      </c>
-      <c r="D53">
-        <v>317</v>
-      </c>
-      <c r="E53">
-        <v>61.1</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Veuf(ve)</t>
-        </is>
-      </c>
-      <c r="D54">
-        <v>49</v>
-      </c>
-      <c r="E54">
         <v>9.4</v>
       </c>
     </row>

--- a/docs/downloads/04/tbl_cm_chars_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_chars_marovoay_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -407,7 +407,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -430,7 +430,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -476,7 +476,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -522,7 +522,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -545,7 +545,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -568,7 +568,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -634,7 +634,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -654,7 +654,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -674,7 +674,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -694,7 +694,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -714,7 +714,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -754,7 +754,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -774,7 +774,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -814,7 +814,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -854,7 +854,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -900,7 +900,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -923,7 +923,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1009,7 +1009,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1032,7 +1032,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1055,7 +1055,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1078,7 +1078,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1095,7 +1095,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1118,7 +1118,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1187,7 +1187,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1227,7 +1227,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1250,7 +1250,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1273,7 +1273,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1342,7 +1342,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1365,7 +1365,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1388,7 +1388,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1411,7 +1411,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1434,7 +1434,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1457,7 +1457,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
